--- a/outputs/daily/hr_rankings_2026-07-14.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-14.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>68.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,7 +808,7 @@
         <v>35.9</v>
       </c>
       <c r="R2" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>66.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1088,7 +1088,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>64.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1368,7 +1368,7 @@
         <v>18.2</v>
       </c>
       <c r="R4" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>63.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1648,7 +1648,7 @@
         <v>18.2</v>
       </c>
       <c r="R5" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>62.4</v>
+        <v>63.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1928,7 +1928,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2184,11 +2184,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>59.4</v>
+        <v>60.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2208,7 +2208,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2488,7 +2488,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>58.6</v>
+        <v>59.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2768,7 +2768,7 @@
         <v>35.9</v>
       </c>
       <c r="R9" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.8</v>
+        <v>53.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3048,7 +3048,7 @@
         <v>35.9</v>
       </c>
       <c r="R10" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52.5</v>
+        <v>53.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3328,7 +3328,7 @@
         <v>18.2</v>
       </c>
       <c r="R11" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>51.5</v>
+        <v>52.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3608,7 +3608,7 @@
         <v>18.2</v>
       </c>
       <c r="R12" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>51.4</v>
+        <v>52.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3888,7 +3888,7 @@
         <v>18.2</v>
       </c>
       <c r="R13" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.8</v>
+        <v>49.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4168,7 +4168,7 @@
         <v>18.2</v>
       </c>
       <c r="R14" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4448,7 +4448,7 @@
         <v>35.9</v>
       </c>
       <c r="R15" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.5</v>
+        <v>45.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -4728,7 +4728,7 @@
         <v>18.2</v>
       </c>
       <c r="R16" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5008,7 +5008,7 @@
         <v>18.2</v>
       </c>
       <c r="R17" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>37.9</v>
+        <v>38.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5288,7 +5288,7 @@
         <v>17.2</v>
       </c>
       <c r="R18" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S18" t="n">
         <v>76.2</v>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.7</v>
+        <v>37.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5568,7 +5568,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>68.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6174,7 +6174,7 @@
         <v>35.9</v>
       </c>
       <c r="R2" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>66.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6454,7 +6454,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>64.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6734,7 +6734,7 @@
         <v>18.2</v>
       </c>
       <c r="R4" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>63.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7014,7 +7014,7 @@
         <v>18.2</v>
       </c>
       <c r="R5" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>62.4</v>
+        <v>63.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7294,7 +7294,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7550,11 +7550,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>59.4</v>
+        <v>60.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7574,7 +7574,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7854,7 +7854,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>58.6</v>
+        <v>59.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8134,7 +8134,7 @@
         <v>35.9</v>
       </c>
       <c r="R9" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.8</v>
+        <v>53.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8414,7 +8414,7 @@
         <v>35.9</v>
       </c>
       <c r="R10" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52.5</v>
+        <v>53.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8694,7 +8694,7 @@
         <v>18.2</v>
       </c>
       <c r="R11" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>51.5</v>
+        <v>52.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8974,7 +8974,7 @@
         <v>18.2</v>
       </c>
       <c r="R12" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>51.4</v>
+        <v>52.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9254,7 +9254,7 @@
         <v>18.2</v>
       </c>
       <c r="R13" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -9440,12 +9440,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.8</v>
+        <v>49.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9534,7 +9534,7 @@
         <v>18.2</v>
       </c>
       <c r="R14" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9814,7 +9814,7 @@
         <v>35.9</v>
       </c>
       <c r="R15" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.5</v>
+        <v>45.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -10094,7 +10094,7 @@
         <v>18.2</v>
       </c>
       <c r="R16" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10374,7 +10374,7 @@
         <v>18.2</v>
       </c>
       <c r="R17" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -10560,12 +10560,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>37.9</v>
+        <v>38.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -10654,7 +10654,7 @@
         <v>17.2</v>
       </c>
       <c r="R18" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S18" t="n">
         <v>76.2</v>
@@ -10840,12 +10840,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.7</v>
+        <v>37.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10934,7 +10934,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
